--- a/output/DP_Member_360/Unit_Test_Cases_Member_360.xlsx
+++ b/output/DP_Member_360/Unit_Test_Cases_Member_360.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="5">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.499</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="13">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.033</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="14">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="26">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="28">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="30">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="32">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.297</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="34">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.34</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="35">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.311</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="36">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="37">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="44">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>test_parse_value_by_type[CHAR(5)-28202-28202]</t>
+          <t>test_parse_value_by_type[CHAR(5)-12345-12345]</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Parse value by type [CHAR(5)-28202-28202]</t>
+          <t>Parse value by type [CHAR(5)-12345-12345]</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="61">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.263</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.229</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="74">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="75">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>0.255</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="86">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.23</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="87">
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>0.305</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="90">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.244</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="92">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="93">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="95">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="98">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0.005</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="99">
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="100">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="101">
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="102">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>0.459</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="103">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>0.004</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="118">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="119">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="129">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="131">
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="H131" s="2" t="n">
-        <v>0.007</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
